--- a/output/full_scan/batch_seq0_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>752.5733955259381</v>
+        <v>952.5733955259381</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>16.15</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>80.73521648178196</v>
+        <v>80.73521648823228</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>53.82825483490927</v>
+        <v>53.82825488033389</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.757339552593801</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.8568610047798604</v>
+        <v>0.8568610047722305</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8390</v>
+        <v>8454</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>751.0854947809411</v>
+        <v>923.2282114724204</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>125</v>
+        <v>353</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.30972259420059</v>
+        <v>92.37873012310057</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46.74472848140428</v>
+        <v>48.02243285926269</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.6085494780941058</v>
+        <v>1.822821147242027</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.1922471979398849</v>
+        <v>15.73374143960916</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8104</v>
+        <v>8926</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>734.0183893414852</v>
+        <v>913.7525610174802</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>43.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.61372651270665</v>
+        <v>67.49700781635983</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31.60228242441764</v>
+        <v>57.43866545502699</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.901838934148518</v>
+        <v>0.8752561017480132</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8172106688004086</v>
+        <v>0.329272613312793</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8182</v>
+        <v>8096</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>726.0397476339307</v>
+        <v>908.7948344907876</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44.9</v>
+        <v>128.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.5497072902374</v>
+        <v>66.40028644151499</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.27270501923731</v>
+        <v>49.45068064799293</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6039747633930643</v>
+        <v>0.8794834490787653</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0387032304449235</v>
+        <v>1.39043770675042</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8089</v>
+        <v>8390</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>686.7172107566777</v>
+        <v>891.0854947809411</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.35</v>
+        <v>125</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.35200096799461</v>
+        <v>73.30972263636855</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.03008510812537</v>
+        <v>46.74472841686964</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.671721075667769</v>
+        <v>0.6085494780941058</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2594126029576485</v>
+        <v>-0.1922471979971041</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8076</v>
+        <v>8089</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>678.7952446234916</v>
+        <v>886.7172107566777</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.2</v>
+        <v>22.35</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>74.32468743305958</v>
+        <v>62.35200064987055</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.208690259672</v>
+        <v>19.03008527512742</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.379524462349156</v>
+        <v>2.671721075667769</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5023245565218289</v>
+        <v>0.2594126039497803</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8096</v>
+        <v>8163</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>678.7948344907877</v>
+        <v>880.6076435019453</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>128.5</v>
+        <v>40.35</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.40028639228387</v>
+        <v>74.88771975514436</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>49.45068063681147</v>
+        <v>54.79240758278995</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8794834490787653</v>
+        <v>0.560764350194533</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.390437706674106</v>
+        <v>0.4234716716882629</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8926</v>
+        <v>8076</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>678.7525610174802</v>
+        <v>878.7952446234916</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.49700781123904</v>
+        <v>74.32468745799279</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>57.43866538359606</v>
+        <v>27.20869029539351</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8752561017480132</v>
+        <v>2.379524462349156</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3292726133414181</v>
+        <v>0.5023245565886101</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8121</v>
+        <v>8104</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>676.6789872210941</v>
+        <v>874.0183893414852</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.75</v>
+        <v>43.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.05919997634979</v>
+        <v>67.61372655633909</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45.38066219740364</v>
+        <v>31.60228244349931</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6678987221094049</v>
+        <v>1.901838934148518</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1616109128682974</v>
+        <v>0.8172106688671867</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8071</v>
+        <v>8105</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>675.9531891318293</v>
+        <v>863.4351020258059</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>21.25</v>
+        <v>20.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.69948167034233</v>
+        <v>72.34908022960985</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>40.5815801670513</v>
+        <v>42.27531250181452</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.595318913182929</v>
+        <v>1.343510202580595</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0901135153396608</v>
+        <v>0.3648487605716868</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8163</v>
+        <v>9103</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>675.6076435019453</v>
+        <v>860</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>40.35</v>
+        <v>5.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>74.88771974291487</v>
+        <v>66.71734833463236</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>54.79240759154613</v>
+        <v>41.16714186003512</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.560764350194533</v>
+        <v>5.042969263653433</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.4234716714974622</v>
+        <v>0.0769423093636761</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8261</v>
+        <v>9906</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>675.0551282897042</v>
+        <v>854.0859380739416</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>171</v>
+        <v>42.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.66031537421118</v>
+        <v>72.74594425320643</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44.68255364021711</v>
+        <v>30.34822589050166</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5055128289704184</v>
+        <v>1.908593807394159</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.8004186699056213</v>
+        <v>1.231793048475554</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8050</v>
+        <v>8070</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>673.6836965855205</v>
+        <v>836.7053431757317</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>57.2</v>
+        <v>62.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.69033220365793</v>
+        <v>76.85229625742122</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>58.67953926065759</v>
+        <v>33.94970418920547</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3683696585520511</v>
+        <v>2.170534317573173</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0307183500495198</v>
+        <v>1.875092071718615</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8289</v>
+        <v>9911</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>673.4177001077212</v>
+        <v>832.9407070104928</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.73459138748893</v>
+        <v>62.87565541351937</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>43.05036005019094</v>
+        <v>20.52801583980833</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3417700107721206</v>
+        <v>1.294070701049283</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.2381427983438353</v>
+        <v>0.3310080046642568</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8105</v>
+        <v>9105</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>663.4351020258059</v>
+        <v>826.0640925842716</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20.4</v>
+        <v>11.45</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>72.34908023187353</v>
+        <v>76.78802958974651</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>42.27531244858802</v>
+        <v>54.73640540846023</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.343510202580595</v>
+        <v>1.606409258427168</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3648487604476711</v>
+        <v>0.5284906782831956</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8150</v>
+        <v>8341</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>662.3560085605787</v>
+        <v>820.5337533471072</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>96.8</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.26722311517765</v>
+        <v>70.51528095496469</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.82847309156265</v>
+        <v>19.44600987772767</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7356008560578736</v>
+        <v>1.553375334710728</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3293254321120837</v>
+        <v>0.3429820255873037</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8088</v>
+        <v>8996</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>661.4981663877343</v>
+        <v>814.6140596363188</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>62.8</v>
+        <v>1125</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.79463350315676</v>
+        <v>52.84171269118709</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.34723730428353</v>
+        <v>11.1577302615153</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6498166387734252</v>
+        <v>0.9614059636318708</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7585692980030161</v>
+        <v>-2.366396064430236</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8081</v>
+        <v>8088</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>659.8235443699132</v>
+        <v>801.4981663877343</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>280.5</v>
+        <v>62.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.98657600539961</v>
+        <v>58.79463348144731</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.57008871432743</v>
+        <v>27.34723720139572</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4823544369913161</v>
+        <v>0.6498166387734252</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.9204038276421967</v>
+        <v>0.7585692984322989</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9906</v>
+        <v>8112</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>654.0859380739416</v>
+        <v>792.7651086855607</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>72.74594413539316</v>
+        <v>60.4358911847369</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.34822585022137</v>
+        <v>22.5432162591375</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.908593807394159</v>
+        <v>1.276510868556064</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.231793048342001</v>
+        <v>0.9655269215593409</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8112</v>
+        <v>8087</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>652.7651086855607</v>
+        <v>786.4781757974417</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.43589116957156</v>
+        <v>62.05574466674944</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.54321619297913</v>
+        <v>24.87813989744192</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.276510868556064</v>
+        <v>0.647817579744179</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.9655269213399158</v>
+        <v>0.2485795913703841</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8070</v>
+        <v>8064</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>636.7053431757317</v>
+        <v>773.7293643828025</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>62.7</v>
+        <v>166</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>76.85229623346409</v>
+        <v>68.32258101243349</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.9497041456388</v>
+        <v>51.80897843058209</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.170534317573173</v>
+        <v>1.872936438280252</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.875092071699543</v>
+        <v>1.905460135585136</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>629.5614978786465</v>
+        <v>769.5614978786465</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>13.85</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.54007694084373</v>
+        <v>55.54007706886257</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>29.88615547635112</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1523273884666107</v>
+        <v>0.1523273884570705</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8454</v>
+        <v>8121</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>628.2282114724203</v>
+        <v>766.6789872210941</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>353</v>
+        <v>40.75</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>92.37873005910016</v>
+        <v>64.05919999346958</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>48.0224328592627</v>
+        <v>45.38066212528738</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.822821147242027</v>
+        <v>0.6678987221094049</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>15.73374144113552</v>
+        <v>-0.1616109128587606</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>9105</v>
+        <v>8472</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>626.0640925842716</v>
+        <v>758.3062406227019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11.45</v>
+        <v>88.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>76.7880295902076</v>
+        <v>69.98141245953876</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>54.73640538855765</v>
+        <v>35.40596354008815</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.606409258427168</v>
+        <v>0.8306240622701884</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5284906782602994</v>
+        <v>2.273185885853648</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8091</v>
+        <v>8473</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>616.4356347831006</v>
+        <v>751.7775420685467</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>241</v>
+        <v>54.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.04982451566297</v>
+        <v>79.09035487695347</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>43.30331781250821</v>
+        <v>52.53774092222247</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6435634783100549</v>
+        <v>1.177754206854676</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-3.888236313456144</v>
+        <v>1.523428884090953</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8109</v>
+        <v>8182</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>614.2406748397896</v>
+        <v>726.0397476339307</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>120</v>
+        <v>44.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.28720847917758</v>
+        <v>58.54970731825544</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.0737394917409</v>
+        <v>24.27270501188548</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4240674839789563</v>
+        <v>0.6039747633930643</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.7670058245875433</v>
+        <v>0.0387032304926182</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8374</v>
+        <v>8049</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>609.1986198993922</v>
+        <v>721.952979128667</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>98.3</v>
+        <v>27.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>50.34221198073434</v>
+        <v>66.01461234818615</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34.17961906045869</v>
+        <v>28.55897151308361</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.919861989939218</v>
+        <v>1.195297912866699</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.633542430951237</v>
+        <v>0.0497520683797803</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8271</v>
+        <v>8109</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>607.4911771382582</v>
+        <v>709.2406748397896</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>222</v>
+        <v>120</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46.08506325170339</v>
+        <v>50.28720852237114</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.04217279917838</v>
+        <v>37.0737395213688</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.249117713825815</v>
+        <v>0.4240674839789563</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-2.178804400724868</v>
+        <v>-0.7670058249691225</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8049</v>
+        <v>8215</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>606.952979128667</v>
+        <v>694.9281308121944</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>27.2</v>
+        <v>29.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>66.01461234818615</v>
+        <v>53.60109518364895</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.55897130301513</v>
+        <v>29.86044263915771</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.195297912866699</v>
+        <v>0.4928130812194393</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0497520683130014</v>
+        <v>0.08709909511609081</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8162</v>
+        <v>9110</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>604.3372080237924</v>
+        <v>690.6991009212185</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>70.7</v>
+        <v>3.95</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.14706522499642</v>
+        <v>74.47499928604054</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>50.14708688634057</v>
+        <v>18.95688504141626</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9337208023792444</v>
+        <v>2.569910092121847</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4444086398997111</v>
+        <v>0.156047964001826</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9911</v>
+        <v>9914</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>602.9407070104928</v>
+        <v>679.7430203883341</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>62.87565538232644</v>
+        <v>61.01281421005194</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.52801580580665</v>
+        <v>32.43417984540264</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.294070701049283</v>
+        <v>0.4743020388334134</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3310080046451779</v>
+        <v>0.1929418684576391</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8215</v>
+        <v>8071</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>599.9281308121944</v>
+        <v>675.9531891318293</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.65</v>
+        <v>21.25</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.60109513616774</v>
+        <v>57.69948168764684</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.86044261354783</v>
+        <v>40.5815801477022</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4928130812194393</v>
+        <v>0.595318913182929</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0870990950779329</v>
+        <v>0.09011351543505509</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8358</v>
+        <v>8261</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>592.5708165856581</v>
+        <v>675.0551282897042</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>596</v>
+        <v>171</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>62.74334453045671</v>
+        <v>60.66031537958566</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.07854765628772</v>
+        <v>44.68255352247506</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2570816585658111</v>
+        <v>0.5055128289704184</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.25488461779996</v>
+        <v>-0.8004186694286393</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8341</v>
+        <v>8084</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>590.5337533471072</v>
+        <v>674.9485989332189</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>79</v>
+        <v>49.65</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>70.51528097236098</v>
+        <v>70.36384455665991</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.44600979764145</v>
+        <v>24.92657121646096</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.553375334710728</v>
+        <v>1.494859893321892</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3429820254537435</v>
+        <v>0.7276598823243582</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9103</v>
+        <v>8050</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>585</v>
+        <v>673.6836965855205</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5.85</v>
+        <v>57.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>66.71734828038096</v>
+        <v>65.69033219785166</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>41.16714173256656</v>
+        <v>58.67953977610576</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5.042969263653433</v>
+        <v>0.3683696585520511</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0769423093445958</v>
+        <v>0.0307183504501953</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8499</v>
+        <v>8289</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>582.5943753312637</v>
+        <v>673.4177001077212</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>292.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.25832865045583</v>
+        <v>59.73459138906357</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.35732744769496</v>
+        <v>43.05035990720779</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2594375331263643</v>
+        <v>0.3417700107721206</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.379846973819301</v>
+        <v>-0.2381427982389006</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8473</v>
+        <v>8150</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>581.7775420685467</v>
+        <v>662.3560085605787</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>54.4</v>
+        <v>96.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>79.09035483944561</v>
+        <v>57.26722312593246</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>52.53774096864</v>
+        <v>29.82847310367497</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.177754206854676</v>
+        <v>0.7356008560578736</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.523428884157725</v>
+        <v>0.329325432045298</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8064</v>
+        <v>8081</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>573.7293643828025</v>
+        <v>659.8235443699132</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>166</v>
+        <v>280.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>68.32258100893</v>
+        <v>56.98657604129473</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>51.80897859983133</v>
+        <v>33.57008873630043</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.872936438280252</v>
+        <v>0.4823544369913161</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.905460135318015</v>
+        <v>-0.920403826974411</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8472</v>
+        <v>8932</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>558.3062406227018</v>
+        <v>659.597131895121</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>88.5</v>
+        <v>102</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>69.98141142130157</v>
+        <v>55.06144162867049</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.40596333592217</v>
+        <v>26.25134741981079</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8306240622701884</v>
+        <v>0.959713189512102</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.273185890241906</v>
+        <v>0.0857627274487136</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8097</v>
+        <v>8072</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>554.0597994299205</v>
+        <v>658.542166611041</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>57.6</v>
+        <v>29.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.26052750255952</v>
+        <v>57.65841789013425</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>41.8813565797219</v>
+        <v>26.82080847044075</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.405979942992056</v>
+        <v>1.354216661104097</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0837757132034606</v>
+        <v>0.3100535741441348</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8227</v>
+        <v>8277</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>552.2841348331208</v>
+        <v>646.8866602039677</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>203</v>
+        <v>10.95</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.98631633143937</v>
+        <v>72.48456933380649</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>35.82656195854099</v>
+        <v>34.59689126347135</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7284134833120739</v>
+        <v>2.188666020396767</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-4.334438508888084</v>
+        <v>0.520576505923404</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8932</v>
+        <v>8102</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>544.597131895121</v>
+        <v>646.864802790317</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>102</v>
+        <v>75.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.0614415614144</v>
+        <v>60.45801596554307</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26.25134734799277</v>
+        <v>17.84569078412902</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.959713189512102</v>
+        <v>1.186480279031697</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0857627273833223</v>
+        <v>1.276671569842821</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8477</v>
+        <v>8429</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>538.4013068334148</v>
+        <v>642.8238544582647</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19.4</v>
+        <v>6.76</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>62.84164227344427</v>
+        <v>62.09973884283954</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>43.31619496171523</v>
+        <v>27.63167416697969</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3401306833414746</v>
+        <v>1.782385445826472</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1073340417610195</v>
+        <v>0.0917120555775795</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8084</v>
+        <v>9907</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>534.9485989332189</v>
+        <v>635.5056104797894</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>49.65</v>
+        <v>16.65</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>70.3638443124953</v>
+        <v>51.07502987932848</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.92657124830926</v>
+        <v>36.78934758005342</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.494859893321892</v>
+        <v>1.050561047978945</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.7276598824960706</v>
+        <v>0.156121779770859</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8087</v>
+        <v>8091</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>526.4781757974417</v>
+        <v>616.4356347831006</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>35.6</v>
+        <v>241</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>62.05574468113824</v>
+        <v>53.04982451566297</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.87813985941161</v>
+        <v>43.30331775008335</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.647817579744179</v>
+        <v>0.6435634783100549</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2485795913608346</v>
+        <v>-3.888236312692946</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8086</v>
+        <v>8374</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>525.4568885016779</v>
+        <v>609.1986198993922</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>156</v>
+        <v>98.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.27094982043988</v>
+        <v>50.3422120342094</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>28.33440988834549</v>
+        <v>34.17961909950519</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5456888501677961</v>
+        <v>0.919861989939218</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.085341883865209</v>
+        <v>-1.633542430894002</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8155</v>
+        <v>8271</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>522.639713500623</v>
+        <v>607.4911771382582</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>371</v>
+        <v>222</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.99869276490304</v>
+        <v>46.08506325801709</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.06161186121621</v>
+        <v>32.04217269261348</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7639713500623022</v>
+        <v>1.249117713825815</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-7.377917104016559</v>
+        <v>-2.178804400658089</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8147</v>
+        <v>9904</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>519.2874928876533</v>
+        <v>607.3817972148757</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>165</v>
+        <v>26.45</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.93785123968239</v>
+        <v>55.27427636280344</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.95251621267974</v>
+        <v>27.768106481255</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4287492887653293</v>
+        <v>1.23817972148757</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.648969536867958</v>
+        <v>0.1802164126585148</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8299</v>
+        <v>8162</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>517.5381220871968</v>
+        <v>604.3372080237924</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2450</v>
+        <v>70.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.82572762459256</v>
+        <v>59.14706525216241</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.30247042459323</v>
+        <v>50.14708682486773</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.253812208719684</v>
+        <v>0.9337208023792444</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-24.95278160328255</v>
+        <v>0.4444086398615505</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8383</v>
+        <v>9910</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>506.4495632301889</v>
+        <v>602.0362599549659</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>58.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.42980609408295</v>
+        <v>57.07092915826971</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.28769358294531</v>
+        <v>26.24568962715945</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6449563230188895</v>
+        <v>2.703625995496591</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1070735005571772</v>
+        <v>1.560999206698416</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8110</v>
+        <v>8171</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>504.9915399589444</v>
+        <v>594.7300540403011</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>56.5</v>
+        <v>24.75</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.20152743986868</v>
+        <v>55.49158913109709</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.74370358167517</v>
+        <v>21.79106335887682</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4991539958944425</v>
+        <v>1.473005404030103</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5312615366112543</v>
+        <v>0.2482643588366484</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8996</v>
+        <v>8358</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>504.6140596363187</v>
+        <v>592.5708165856581</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1125</v>
+        <v>596</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.8417126773278</v>
+        <v>62.74334452952526</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.15773029972303</v>
+        <v>32.07854757244512</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9614059636318708</v>
+        <v>0.2570816585658111</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-2.366396064716476</v>
+        <v>2.254884618276925</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8131</v>
+        <v>8499</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>502.9087032540666</v>
+        <v>582.5943753312637</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>292.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.23390452884819</v>
+        <v>49.25832869367294</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.79412470194558</v>
+        <v>20.35732741669294</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7908703254066559</v>
+        <v>0.2594375331263643</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4469288759723915</v>
+        <v>-2.379846974296292</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>9110</v>
+        <v>8101</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>490.6991009212185</v>
+        <v>577.4358974358975</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>3.95</v>
+        <v>16.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>74.47499928775071</v>
+        <v>65.98294731730547</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.95688504027773</v>
+        <v>19.52478211264034</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.569910092121847</v>
+        <v>0.2435897435897435</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1560479639999178</v>
+        <v>0.3490128764627827</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8455</v>
+        <v>8085</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>489.127392695092</v>
+        <v>575</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>33.35</v>
+        <v>14.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.74146452654156</v>
+        <v>62.06258415113756</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>38.8379527580683</v>
+        <v>40.28260932186734</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.4127392695092</v>
+        <v>6.7421167195268</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.090002000996336</v>
+        <v>0.5723952007224828</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8072</v>
+        <v>8069</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>488.542166611041</v>
+        <v>566.5319890718836</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>29.4</v>
+        <v>214</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>57.65841786263108</v>
+        <v>54.1484014858617</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.82080838567954</v>
+        <v>43.34258063578425</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.354216661104097</v>
+        <v>0.653198907188356</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3100535735145132</v>
+        <v>-3.791341391171265</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8291</v>
+        <v>8478</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>476.0228966628194</v>
+        <v>561.7364954459492</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>71</v>
+        <v>162.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.34319465916347</v>
+        <v>57.47121730419551</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.63261053066668</v>
+        <v>19.33408775071912</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1022896662819363</v>
+        <v>2.173649544594918</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-4.555249709722183</v>
+        <v>1.384000456808474</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8429</v>
+        <v>8481</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>472.8238544582647</v>
+        <v>560.4134924500074</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>6.76</v>
+        <v>41.35</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>62.09973876177272</v>
+        <v>58.09224364548882</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.63167400183621</v>
+        <v>20.53412198194771</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.782385445826472</v>
+        <v>0.5413492450007352</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0917120555604078</v>
+        <v>0.1513746010781411</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8114</v>
+        <v>8097</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>471.902620390572</v>
+        <v>554.0597994299205</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>229</v>
+        <v>57.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.08840495227329</v>
+        <v>55.26052723183135</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>42.92785160019112</v>
+        <v>41.88135671446704</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6902620390571964</v>
+        <v>0.405979942992056</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-3.213404130671712</v>
+        <v>0.0837757139857235</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8069</v>
+        <v>8210</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>471.5319890718836</v>
+        <v>554.0485521249502</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>214</v>
+        <v>1370</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.14840157029362</v>
+        <v>53.31484363669495</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>43.34258032480654</v>
+        <v>34.07987828931022</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.653198907188356</v>
+        <v>0.9048552124950257</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-3.791341395273321</v>
+        <v>-13.71314230113656</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8234</v>
+        <v>8227</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>468.6750197749655</v>
+        <v>552.2841348331208</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>69.2</v>
+        <v>203</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.38652964696944</v>
+        <v>50.98631637138772</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>29.90455145051475</v>
+        <v>35.82656193881908</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8675019774965467</v>
+        <v>0.7284134833120739</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.3503368047020074</v>
+        <v>-4.334438508506491</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9904</v>
+        <v>8464</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>467.3817972148757</v>
+        <v>539.5543758963415</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>26.45</v>
+        <v>328.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.27427622265697</v>
+        <v>49.81681726086444</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.7681063448474</v>
+        <v>27.39786710883888</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.23817972148757</v>
+        <v>0.4554375896341598</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1802164126012763</v>
+        <v>3.164204118968588</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8210</v>
+        <v>8477</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>459.0485521249503</v>
+        <v>538.4013068334148</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1370</v>
+        <v>19.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.31484362969082</v>
+        <v>62.84164232297334</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>34.07987831968179</v>
+        <v>43.31619497733345</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9048552124950257</v>
+        <v>0.3401306833414746</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-13.71314230113656</v>
+        <v>0.1073340417610195</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8249</v>
+        <v>8422</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>457.9273895448429</v>
+        <v>536.2840909375028</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>53.3</v>
+        <v>28.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.145418657931</v>
+        <v>54.28368608073907</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>25.16676410278108</v>
+        <v>16.42669649518257</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2927389544842931</v>
+        <v>1.128409093750284</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0077830155822959</v>
+        <v>0.2822050030707027</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8171</v>
+        <v>8086</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>454.730054040301</v>
+        <v>525.4568885016779</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>24.75</v>
+        <v>156</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>55.49158897541152</v>
+        <v>49.27094980148942</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.79106326068774</v>
+        <v>28.33440969308613</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.473005404030103</v>
+        <v>0.5456888501677961</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2482643587603297</v>
+        <v>-1.08534188310202</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8487</v>
+        <v>8155</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>450.2344811961939</v>
+        <v>522.639713500623</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.70706787464933</v>
+        <v>40.99869281963751</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>20.90952434636388</v>
+        <v>22.06161172104489</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.023448119619393</v>
+        <v>0.7639713500623022</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0643485524851113</v>
+        <v>-7.377917103730331</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>9914</v>
+        <v>8147</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>449.7430203883341</v>
+        <v>519.2874928876533</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>165</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>61.01281422682305</v>
+        <v>46.93785127629743</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32.4341795695683</v>
+        <v>20.95251609340417</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4743020388334134</v>
+        <v>0.4287492887653293</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1929418678852552</v>
+        <v>-2.648969536524521</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8277</v>
+        <v>8299</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>446.8866602039677</v>
+        <v>517.6661168722344</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>10.95</v>
+        <v>2450</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>72.48456931691754</v>
+        <v>50.82572762328134</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>34.59689128642679</v>
+        <v>23.30247038636874</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.188666020396767</v>
+        <v>1.266611687223436</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.5205765059329437</v>
+        <v>-24.9527816008019</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8102</v>
+        <v>8383</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>446.864802790317</v>
+        <v>506.4495632301889</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>75.7</v>
+        <v>58.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>60.45801597234068</v>
+        <v>49.42980612609201</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.84569066430063</v>
+        <v>22.287693605004</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.186480279031697</v>
+        <v>0.6449563230188895</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.276671569728341</v>
+        <v>-0.1070735003663873</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8481</v>
+        <v>8110</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>445.4134924500074</v>
+        <v>504.9915399589444</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>41.35</v>
+        <v>56.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>58.09224358876602</v>
+        <v>53.20152743986868</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.53412199516102</v>
+        <v>20.7437035349039</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5413492450007352</v>
+        <v>0.4991539958944425</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1513746007728746</v>
+        <v>0.5312615366971176</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8213</v>
+        <v>8093</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>439.1331640273501</v>
+        <v>504.8922903076686</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>37.1</v>
+        <v>18.25</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.32046764977146</v>
+        <v>48.04014154997447</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.05147122161573</v>
+        <v>5.535970994801467</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4133164027350122</v>
+        <v>0.4892290307668601</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2576503028389106</v>
+        <v>-0.001028917084088</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8074</v>
+        <v>8404</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>424.4736994512151</v>
+        <v>503.4127100712389</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>17.45</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.2963048964933</v>
+        <v>56.01011800626491</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.00544704098142</v>
+        <v>22.00987911066243</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4473699451215125</v>
+        <v>1.341271007123892</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.9232105236000224</v>
+        <v>0.2030347704750045</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8438</v>
+        <v>8131</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>422.6319518684523</v>
+        <v>502.9087032540666</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>83.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.71790713711068</v>
+        <v>52.23390454754426</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.3073530848891</v>
+        <v>15.79412466081605</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2631951868452263</v>
+        <v>0.7908703254066559</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.150100551218881</v>
+        <v>0.4469288759723915</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>9907</v>
+        <v>8455</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>420.5056104797894</v>
+        <v>489.127392695092</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>16.65</v>
+        <v>33.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.07502984548884</v>
+        <v>46.74146453927936</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>36.78934749484123</v>
+        <v>38.8379527909831</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.050561047978945</v>
+        <v>1.4127392695092</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1561217796945431</v>
+        <v>-1.090002000929553</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8466</v>
+        <v>9912</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>411.1254777792065</v>
+        <v>476.2826081673391</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.4</v>
+        <v>12.55</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>55.81128196534145</v>
+        <v>52.57594568523973</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>35.94217891463537</v>
+        <v>9.027381712115631</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1125477779206529</v>
+        <v>0.1282608167339079</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.2813029911713425</v>
+        <v>0.0078966213478133</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8464</v>
+        <v>8291</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>399.5543758963416</v>
+        <v>476.0228966628194</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>328.5</v>
+        <v>71</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.81681743087299</v>
+        <v>49.34313598993002</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>27.39786692265175</v>
+        <v>38.63208873246461</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4554375896341598</v>
+        <v>0.1022896662819363</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>3.164204115152726</v>
+        <v>-4.55524853658525</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8092</v>
+        <v>8114</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>397.4643986275469</v>
+        <v>471.902620390572</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.3</v>
+        <v>229</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.83658624410784</v>
+        <v>50.08840504693766</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>31.35763349443335</v>
+        <v>42.92785170987715</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7464398627546875</v>
+        <v>0.6902620390571964</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.2690134880721406</v>
+        <v>-3.213404130957898</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8478</v>
+        <v>8234</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>391.7364954459492</v>
+        <v>468.6750197749655</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>162.5</v>
+        <v>69.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>57.47121703902802</v>
+        <v>49.38652971552082</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.33408774906366</v>
+        <v>29.90455146229161</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.173649544594918</v>
+        <v>0.8675019774965467</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.38400045719005</v>
+        <v>-0.3503368043204342</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8093</v>
+        <v>8059</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>389.8922903076686</v>
+        <v>467.2448977744669</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18.25</v>
+        <v>20.05</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.04014147097282</v>
+        <v>52.47633023201119</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5.535971226664677</v>
+        <v>24.16877619603736</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4892290307668601</v>
+        <v>0.7244897774466886</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.001028917084088</v>
+        <v>0.1052185923396036</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8101</v>
+        <v>8249</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>377.4358974358975</v>
+        <v>457.9273895448429</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>16.2</v>
+        <v>53.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>65.98294735414915</v>
+        <v>51.14541869888318</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.52478209831474</v>
+        <v>25.16676406024589</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2435897435897435</v>
+        <v>0.2927389544842931</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.349012876405544</v>
+        <v>-0.0077830153724234</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8085</v>
+        <v>8488</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>375</v>
+        <v>451.2455644340414</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14.7</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>62.06258402458819</v>
+        <v>50.95442572320238</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>40.28260919883496</v>
+        <v>8.963033658458619</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>6.7421167195268</v>
+        <v>0.1245564434041411</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.5723952007224828</v>
+        <v>0.0677909806801395</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8103</v>
+        <v>8487</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>365.207955688025</v>
+        <v>450.2344811961939</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.95508527683659</v>
+        <v>52.70706798909379</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.93559207069832</v>
+        <v>20.90952472244997</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5207955688025036</v>
+        <v>1.023448119619393</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.136423778126863</v>
+        <v>-0.0643485526568198</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9912</v>
+        <v>9908</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>361.2826081673391</v>
+        <v>447.852900891463</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.55</v>
+        <v>29.45</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.57594565776018</v>
+        <v>54.28443991906266</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.027381706022709</v>
+        <v>15.34277665813694</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1282608167339079</v>
+        <v>0.7852900891463009</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.007896621319195</v>
+        <v>0.0568305074042572</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8488</v>
+        <v>8213</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>361.2455644340414</v>
+        <v>439.1331640273501</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>37.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.95442570914412</v>
+        <v>45.320467613307</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8.963033687101882</v>
+        <v>20.05147122701521</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1245564434041411</v>
+        <v>0.4133164027350122</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.06779098068967949</v>
+        <v>-0.2576503026576542</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9910</v>
+        <v>8074</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>337.0362599549659</v>
+        <v>424.4736994512151</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>57.07092920430698</v>
+        <v>44.29630490567173</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26.24568948378561</v>
+        <v>13.00544700005361</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.703625995496591</v>
+        <v>0.4473699451215125</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1.560999206030644</v>
+        <v>-0.9232105235714156</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8404</v>
+        <v>8438</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>333.4127100712389</v>
+        <v>422.6319518684523</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>17.45</v>
+        <v>83.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>56.01011782343399</v>
+        <v>42.71790712978817</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.00987898972885</v>
+        <v>18.30735295617805</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.341271007123892</v>
+        <v>0.2631951868452263</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2030347704559261</v>
+        <v>-1.15010055098993</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8059</v>
+        <v>8183</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>327.2448977744669</v>
+        <v>417.9757361068092</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>20.05</v>
+        <v>32.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.476330077803</v>
+        <v>51.85498115668447</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>24.16877619410773</v>
+        <v>14.35220629671756</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7244897774466886</v>
+        <v>0.7975736106809169</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1052185922823689</v>
+        <v>0.2843410235543405</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>322.1686368729368</v>
+        <v>414.3532286061565</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>12.1</v>
+        <v>22.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.2887941396672</v>
+        <v>58.75254571318239</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.01568368672618</v>
+        <v>16.43697016394791</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2168636872936735</v>
+        <v>0.4353228606156527</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0157336453760598</v>
+        <v>0.1664414183303869</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8067</v>
+        <v>8443</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>314.8697963747882</v>
+        <v>413.2500942999854</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.85869594219335</v>
+        <v>47.01562065572263</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.190035578885899</v>
+        <v>63.08270690001964</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.486979637478824</v>
+        <v>0.3250094299985368</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0683332343101703</v>
+        <v>0.0217389153132167</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>9905</v>
+        <v>9802</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>313.6580296374736</v>
+        <v>411.5620541036819</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>20.65</v>
+        <v>79</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.9970321665255</v>
+        <v>54.24668906938279</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.89837538843875</v>
+        <v>18.70981999905497</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.865802963747358</v>
+        <v>0.6562054103681956</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0001207364495465</v>
+        <v>0.6752051749021259</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8440</v>
+        <v>8466</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>309.304733185047</v>
+        <v>411.1254777792065</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>23.15</v>
+        <v>16.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>52.09574779004851</v>
+        <v>55.81128201675448</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.77218039235716</v>
+        <v>35.94217954927962</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4304733185047037</v>
+        <v>0.1125477779206529</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.103440467375085</v>
+        <v>0.281302991467074</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8422</v>
+        <v>8442</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>306.2840909375028</v>
+        <v>406.5185092597602</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>28.1</v>
+        <v>41.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.2836851778034</v>
+        <v>38.31639210974289</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.42669649518257</v>
+        <v>34.13135859112829</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.128409093750284</v>
+        <v>1.65185092597602</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2822050040516656</v>
+        <v>0.3808020464674166</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8054</v>
+        <v>9905</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>304.8377284964112</v>
+        <v>403.6580296374736</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>100.5</v>
+        <v>20.65</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.3841695878589</v>
+        <v>40.99703232589853</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.2471175470475</v>
+        <v>20.8983755786483</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4837728496411155</v>
+        <v>1.865802963747358</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.884551165148068</v>
+        <v>0.0001207364400065</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8183</v>
+        <v>8092</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>302.9757361068092</v>
+        <v>397.4643986275469</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>32.8</v>
+        <v>16.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.8549811052096</v>
+        <v>44.83658629757153</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.3522062315112</v>
+        <v>31.35763349673298</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7975736106809169</v>
+        <v>0.7464398627546875</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.284341023449401</v>
+        <v>-0.2690134880721406</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8463</v>
+        <v>9902</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>299.3532286061565</v>
+        <v>388.3435406302575</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>22.4</v>
+        <v>14.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>58.75254566756801</v>
+        <v>51.62088607543956</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.43697003141231</v>
+        <v>15.53043363691846</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4353228606156527</v>
+        <v>1.334354063025748</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1664414182445306</v>
+        <v>0.0994144868950784</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8111</v>
+        <v>8240</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>289.9565932789651</v>
+        <v>373.5127801988082</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>61.8</v>
+        <v>59.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.48480603358976</v>
+        <v>40.39776135787727</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.58849267963798</v>
+        <v>17.04414236774221</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4956593278965123</v>
+        <v>0.3512780198808226</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2281120132640119</v>
+        <v>-0.8712440629131587</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8240</v>
+        <v>8103</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>283.5127801988082</v>
+        <v>365.207955688025</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>59.7</v>
+        <v>101</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.39776130646923</v>
+        <v>43.95508529456518</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.0441423585431</v>
+        <v>14.93559209681614</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3512780198808226</v>
+        <v>0.5207955688025036</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.871244062884541</v>
+        <v>-1.136423777799862</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8442</v>
+        <v>8222</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>266.5185092597602</v>
+        <v>355.7698244113187</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>41.55</v>
+        <v>36.85</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>38.31639202001013</v>
+        <v>52.37118796720809</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>34.13135824583316</v>
+        <v>19.25223278747419</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.65185092597602</v>
+        <v>0.5769824411318683</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3808020462384629</v>
+        <v>0.1968469845629328</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9902</v>
+        <v>8176</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>248.3435406302575</v>
+        <v>355.627604850503</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14.2</v>
+        <v>10.35</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.62088591433798</v>
+        <v>50.84794420509528</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.53043349272142</v>
+        <v>12.93026712206928</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.334354063025748</v>
+        <v>0.5627604850502973</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.09941448688553869</v>
+        <v>0.0720182397758547</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>9908</v>
+        <v>8467</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>242.852900891463</v>
+        <v>351.3796945051245</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>29.45</v>
+        <v>129.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>54.28443987079691</v>
+        <v>41.90339136918447</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.34277659773382</v>
+        <v>19.70542115062434</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7852900891463009</v>
+        <v>0.137969450512449</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0568305073851773</v>
+        <v>1.073957070971293</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>9802</v>
+        <v>8411</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>241.562054103682</v>
+        <v>322.1686368729368</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>79</v>
+        <v>12.1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>54.24668888786084</v>
+        <v>49.28879435270869</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.70981993669159</v>
+        <v>21.01568353848445</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6562054103681956</v>
+        <v>0.2168636872936735</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.6752051747304058</v>
+        <v>0.0157336453188211</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8222</v>
+        <v>8067</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>240.7698244113187</v>
+        <v>314.8697963747882</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>36.85</v>
+        <v>13.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.37118773485842</v>
+        <v>51.85869592827154</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.25223275628419</v>
+        <v>8.190035539948106</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5769824411318683</v>
+        <v>1.486979637478824</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1968469847918916</v>
+        <v>0.0683332343769469</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8176</v>
+        <v>8476</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>240.627604850503</v>
+        <v>311.5287793284289</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>10.35</v>
+        <v>15.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.84794402235304</v>
+        <v>40.14022119068666</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.93026712988924</v>
+        <v>28.0249760669023</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5627604850502973</v>
+        <v>0.6528779328428868</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.07201823971861809</v>
+        <v>0.0977675089229508</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8467</v>
+        <v>8440</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>236.3796945051245</v>
+        <v>309.304733185047</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>129.5</v>
+        <v>23.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.90339096415055</v>
+        <v>52.095747822852</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.70542102329299</v>
+        <v>22.77218050959017</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.137969450512449</v>
+        <v>0.4304733185047037</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>1.073957071162087</v>
+        <v>0.103440467556338</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8482</v>
+        <v>8054</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>235</v>
+        <v>304.8377284964112</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>14.29917096805789</v>
+        <v>42.38416966695256</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.005992409395041</v>
+        <v>13.24711751342368</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0</v>
+        <v>0.4837728496411155</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-3.126133077829134</v>
+        <v>-0.884551164766487</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8431</v>
+        <v>8111</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>224.9477365389835</v>
+        <v>289.9565932789651</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>54.3</v>
+        <v>61.8</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.05229130295616</v>
+        <v>41.48480613307449</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.446080367272485</v>
+        <v>14.58849255180045</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4947736538983495</v>
+        <v>0.4956593278965123</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1246653999143103</v>
+        <v>-0.2281120131113768</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8443</v>
+        <v>8940</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>208.2500942999854</v>
+        <v>289.1688671881487</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>11.4</v>
+        <v>16.85</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.01562069092883</v>
+        <v>44.16402354075638</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>63.08270693192425</v>
+        <v>14.57798545429725</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3250094299985368</v>
+        <v>1.416886718814874</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0217389152845958</v>
+        <v>0.0344843033231151</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8476</v>
+        <v>9930</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>196.5287793284289</v>
+        <v>282.893841561088</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>15.75</v>
+        <v>69.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.14022141078075</v>
+        <v>54.24158130335257</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>28.02497577542593</v>
+        <v>18.78728855508607</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6528779328428868</v>
+        <v>0.7893841561088</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0977675087512369</v>
+        <v>0.2394109677595747</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8080</v>
+        <v>9955</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>193.6681391538685</v>
+        <v>282.3630244019039</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.09606968241688</v>
+        <v>44.38508184429401</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>29.2900513321862</v>
+        <v>16.68211794386016</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3668139153868532</v>
+        <v>0.7363024401903943</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0874277583702753</v>
+        <v>0.1637322812906335</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8367</v>
+        <v>8410</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>185.8650291909339</v>
+        <v>268.2597329667371</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>41</v>
+        <v>35.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.68974229252084</v>
+        <v>48.10640162191423</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.3175851934636</v>
+        <v>21.98493584140738</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.08650291909339</v>
+        <v>1.325973296673716</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0802833737960231</v>
+        <v>0.1625869167032508</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8940</v>
+        <v>8482</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>174.1688671881487</v>
+        <v>235</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>16.85</v>
+        <v>0</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.16402350882347</v>
+        <v>14.29917098693629</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.57798527450338</v>
+        <v>8.005992413051398</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.416886718814874</v>
+        <v>0</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0344843031514017</v>
+        <v>-3.126133077352151</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>9930</v>
+        <v>8431</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>167.893841561088</v>
+        <v>224.9477365389835</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.5</v>
+        <v>54.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>54.24158110489076</v>
+        <v>38.05229123921042</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.78728854895319</v>
+        <v>9.44608050794811</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7893841561088</v>
+        <v>0.4947736538983495</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2394109678740453</v>
+        <v>-0.1246653992656114</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>9955</v>
+        <v>8068</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>167.3630244019039</v>
+        <v>211.2798758690112</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>28.4</v>
+        <v>20</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.38508169231353</v>
+        <v>38.67246413077078</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.68211805274623</v>
+        <v>15.5452361229506</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7363024401903943</v>
+        <v>0.6279875869011206</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1637322812906335</v>
+        <v>0.0248857088534794</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8410</v>
+        <v>8080</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>128.2597329667371</v>
+        <v>193.6681391538685</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>35.2</v>
+        <v>28</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.10640130763962</v>
+        <v>48.09606961324366</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>21.98493564060922</v>
+        <v>29.29005167185631</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.325973296673716</v>
+        <v>0.3668139153868532</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1625869167414112</v>
+        <v>0.08742775849429051</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8462</v>
+        <v>8367</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>99.42473012390479</v>
+        <v>185.8650291909339</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>139.5</v>
+        <v>41</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.18982827511027</v>
+        <v>37.68974270522981</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.90695160625505</v>
+        <v>24.31758520620373</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9424730123904788</v>
+        <v>1.08650291909339</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1304595673254083</v>
+        <v>0.08028337392004049</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8068</v>
+        <v>8462</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>96.27987586901121</v>
+        <v>99.42473012390479</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>20</v>
+        <v>139.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.67246373748494</v>
+        <v>45.18982850597749</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.54523612424004</v>
+        <v>16.90695161195697</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6279875869011206</v>
+        <v>0.9424730123904788</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0248857089393373</v>
+        <v>0.1304595668484018</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.64739048916685</v>
+        <v>47.64739042301493</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9.7555580050866</v>
+        <v>9.755558031120389</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.5164699365065837</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0380879485063239</v>
+        <v>0.0380879485540236</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
